--- a/NotasGeologiaPublicationList_UpdateNotasGeologiaPublicationList_Updated_1.xlsx
+++ b/NotasGeologiaPublicationList_UpdateNotasGeologiaPublicationList_Updated_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\castr\Documents\GitHub\mariantoc.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E3E6038-CE3E-4065-9F9C-781AA7896D91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23CA9D1B-27FF-4D86-AD01-EB9E48CDB92C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9F60C23B-EB8B-4BF1-B197-717718F4FFB2}"/>
   </bookViews>
